--- a/doc/_static/example-files/PMHC-5-0-combined.xlsx
+++ b/doc/_static/example-files/PMHC-5-0-combined.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennib/Work/git/PMHC/spec/doc/_static/example-files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57C8717-27C5-9B47-86C4-8C5E9160293D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="29180" windowHeight="17840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -29,12 +35,12 @@
     <sheet name="SIDAS" sheetId="20" r:id="rId20"/>
     <sheet name="WHO-5" sheetId="21" r:id="rId21"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="404">
   <si>
     <t>key</t>
   </si>
@@ -1251,8 +1257,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1289,13 +1295,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1333,7 +1347,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1367,6 +1381,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1401,9 +1416,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1576,11 +1592,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1588,7 +1604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1610,11 +1626,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1646,7 +1662,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1675,7 +1691,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1704,7 +1720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1733,7 +1749,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1762,7 +1778,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1791,7 +1807,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1820,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1849,7 +1865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1878,7 +1894,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1907,7 +1923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1942,11 +1958,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:BB22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:54">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2110,7 +2126,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:54">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2271,7 +2287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:54">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2432,7 +2448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:54">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2593,7 +2609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:54">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2754,7 +2770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:54">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2915,7 +2931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:54">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3076,7 +3092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:54">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3237,7 +3253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:54">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3398,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:54">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -3559,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3720,7 +3736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:54">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -3881,7 +3897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:54">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4042,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:54">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -4203,7 +4219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:54">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -4364,7 +4380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:54">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -4525,7 +4541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -4686,7 +4702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -4847,7 +4863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -5008,7 +5024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -5169,7 +5185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -5330,7 +5346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -5497,11 +5513,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5560,7 +5576,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -5616,7 +5632,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -5672,7 +5688,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5728,7 +5744,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -5784,7 +5800,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -5840,7 +5856,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -5896,7 +5912,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -5952,7 +5968,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6008,7 +6024,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6064,7 +6080,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6126,11 +6142,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6147,7 +6163,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6164,7 +6180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6181,7 +6197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6198,7 +6214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6215,7 +6231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -6232,7 +6248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6249,7 +6265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -6266,7 +6282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6283,7 +6299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6300,7 +6316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6317,7 +6333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -6334,7 +6350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -6357,11 +6373,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6390,7 +6406,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6416,7 +6432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6442,7 +6458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6468,7 +6484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6494,7 +6510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -6520,7 +6536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6546,7 +6562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -6572,7 +6588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6598,7 +6614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6624,7 +6640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6656,11 +6672,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6701,7 +6717,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6742,7 +6758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6789,11 +6805,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6810,7 +6826,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6827,7 +6843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6844,7 +6860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6861,7 +6877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6878,7 +6894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -6901,11 +6917,11 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6922,7 +6938,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6945,11 +6961,11 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6966,7 +6982,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6986,11 +7002,11 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -7007,7 +7023,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7021,7 +7037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -7035,7 +7051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -7055,11 +7071,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -7094,7 +7110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7129,11 +7145,11 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -7162,7 +7178,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7188,7 +7204,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -7220,11 +7236,11 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -7253,7 +7269,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7279,7 +7295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -7311,11 +7327,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -7350,7 +7366,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7382,7 +7398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -7414,7 +7430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -7446,7 +7462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -7478,7 +7494,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -7510,7 +7526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -7548,11 +7564,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -7584,19 +7600,22 @@
         <v>48</v>
       </c>
       <c r="K1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" t="s">
         <v>49</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>50</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>51</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7628,16 +7647,19 @@
         <v>9</v>
       </c>
       <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <v>27072021</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>54</v>
       </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -7669,16 +7691,19 @@
         <v>1</v>
       </c>
       <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <v>21062021</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>21</v>
       </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="N3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -7710,16 +7735,19 @@
         <v>1</v>
       </c>
       <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>30082021</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>57</v>
       </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="N4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -7751,16 +7779,19 @@
         <v>1</v>
       </c>
       <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
         <v>3082021</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>59</v>
       </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="N5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -7791,8 +7822,11 @@
       <c r="J6">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -7823,8 +7857,11 @@
       <c r="J7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="K7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -7856,16 +7893,19 @@
         <v>2</v>
       </c>
       <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
         <v>10092021</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>63</v>
       </c>
-      <c r="M8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="N8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -7896,8 +7936,11 @@
       <c r="J9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="K9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -7928,8 +7971,11 @@
       <c r="J10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="K10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7960,8 +8006,11 @@
       <c r="J11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="K11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -7991,6 +8040,9 @@
       </c>
       <c r="J12">
         <v>2</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7999,11 +8051,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -8053,7 +8105,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8100,7 +8152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -8147,7 +8199,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -8194,7 +8246,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -8241,7 +8293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -8288,7 +8340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -8335,7 +8387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -8382,7 +8434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -8429,7 +8481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -8476,7 +8528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -8523,7 +8575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -8576,11 +8628,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AE11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -8636,10 +8688,10 @@
         <v>110</v>
       </c>
       <c r="S1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T1" t="s">
         <v>111</v>
-      </c>
-      <c r="T1" t="s">
-        <v>48</v>
       </c>
       <c r="U1" t="s">
         <v>112</v>
@@ -8675,7 +8727,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8767,7 +8819,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -8823,10 +8875,10 @@
         <v>4</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3">
         <v>303</v>
@@ -8862,7 +8914,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -8954,7 +9006,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -9010,10 +9062,10 @@
         <v>3</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5">
         <v>402</v>
@@ -9046,7 +9098,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -9138,7 +9190,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9191,10 +9243,10 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <v>205</v>
@@ -9227,7 +9279,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9319,7 +9371,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -9411,7 +9463,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -9503,7 +9555,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -9556,10 +9608,10 @@
         <v>1</v>
       </c>
       <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
         <v>9</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
       </c>
       <c r="U11">
         <v>102</v>
@@ -9598,11 +9650,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -9616,7 +9668,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -9630,7 +9682,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9644,7 +9696,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9658,7 +9710,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -9672,7 +9724,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -9686,7 +9738,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9700,7 +9752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9714,7 +9766,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -9728,7 +9780,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -9742,7 +9794,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -9762,11 +9814,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -9786,7 +9838,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -9803,7 +9855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9820,7 +9872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9837,7 +9889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -9854,7 +9906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -9871,7 +9923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9888,7 +9940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9905,7 +9957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -9922,7 +9974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -9939,7 +9991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -9956,7 +10008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -9973,7 +10025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -9990,7 +10042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -10007,7 +10059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -10024,7 +10076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -10041,7 +10093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -10058,7 +10110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -10075,7 +10127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -10092,7 +10144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -10109,7 +10161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -10126,7 +10178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -10149,11 +10201,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -10212,7 +10264,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -10268,7 +10320,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -10324,7 +10376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -10380,7 +10432,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -10436,7 +10488,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
